--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-organization.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$83</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="563">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T17:27:39+00:00</t>
+    <t>2026-02-05T18:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire</t>
+    <t>http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-pop-exp</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -269,10 +269,10 @@
 </t>
   </si>
   <si>
-    <t>A structured set of questions</t>
-  </si>
-  <si>
-    <t>A structured set of questions intended to guide the collection of answers from end-users. Questionnaires provide detailed control over order, presentation, phraseology and grouping to allow coherent, consistent data collection.</t>
+    <t>Populatable Questionnaire - Expression</t>
+  </si>
+  <si>
+    <t>Defines elements that support auto-population and pre-population of questionnaires using the Expression-based population mechanism.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -486,58 +486,78 @@
 </t>
   </si>
   <si>
-    <t>Questionnaire.extension:designNote</t>
-  </si>
-  <si>
-    <t>designNote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {designNote}
+    <t>Questionnaire.extension:library</t>
+  </si>
+  <si>
+    <t>library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {cqf-library}
 </t>
   </si>
   <si>
-    <t>Design comments</t>
-  </si>
-  <si>
-    <t>Information captured by the author/maintainer of the questionnaire for development purposes, not intended to be seen by users.</t>
-  </si>
-  <si>
-    <t>Allows capture of todos, rationale for design decisions, etc.  It can also be used to capture comments about the completion of the form in general. Allows commentary to be captured during the process of answering a questionnaire (if not already supported by the form design) as well as after the form is completed. Comments are not part of the "data" of the form. If a form prompts for a comment, this should be captured in an answer, not in this element. Formal assessments of the QuestionnaireResponse would use [[[Observation]]].</t>
-  </si>
-  <si>
-    <t>Questionnaire.extension:performerType</t>
-  </si>
-  <si>
-    <t>performerType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-performerType}
+    <t>A library containing logic used by the artifact</t>
+  </si>
+  <si>
+    <t>A reference to a library containing cql used in this Questionnaire.</t>
+  </si>
+  <si>
+    <t>For questionnaires, see additional guidance and examples in the [SDC implementation guide](http://hl7.org/fhir/uv/sdc/behavior.html#cqf-library).</t>
+  </si>
+  <si>
+    <t>Questionnaire.extension:launchContext</t>
+  </si>
+  <si>
+    <t>launchContext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-launchContext}
 </t>
   </si>
   <si>
-    <t>Resource that can record answers to this Questionnaire</t>
-  </si>
-  <si>
-    <t>Indicates the types of resources that can record answers to a Questionnaire. Open Issue: Should this extension be moved to core?</t>
-  </si>
-  <si>
-    <t>Questionnaire.extension:assemble-expectation</t>
-  </si>
-  <si>
-    <t>assemble-expectation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-assemble-expectation}
+    <t>Context resources needed for Questionnaire</t>
+  </si>
+  <si>
+    <t>Resources that provide context for form processing logic (pre-population, flow-control, drop-down selection, etc.) when creating/displaying/editing a QuestionnaireResponse.</t>
+  </si>
+  <si>
+    <t>3 of these launch contexts are aligned with the existing SMART on FHIR "launch" contexts.</t>
+  </si>
+  <si>
+    <t>Questionnaire.extension:itemPopulationContext</t>
+  </si>
+  <si>
+    <t>itemPopulationContext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-itemPopulationContext}
 </t>
   </si>
   <si>
-    <t>Questionnaire is modular</t>
-  </si>
-  <si>
-    <t>If present, indicates that this questionnaire has expectations with respect to assembly.  Specifically, indicates whether this form requires assembly (i.e. it can't be used directly without invoking the [$assemble](http://hl7.org/fhir/uv/sdc/2025Jan/OperationDefinition-Questionnaire-assemble.html) operation operation on it) and/or whether it is intended for use only as a 'child' in an assembly process.  The assembly processs might mean filling in item metadata based on information looked up from item.definitions and/or retrieving sub-questionnaires pointed to by [sub-questionnaire](http://hl7.org/fhir/uv/sdc/2025Jan/StructureDefinition-sdc-questionnaire-subQuestionnaire.html) extensions.</t>
-  </si>
-  <si>
-    <t>SDC-conformant Questionnaires **SHALL** declare this extension if they require an assembly process prior to use.  If not declared, then the Questionnaire is not necessarily safe for use as a child form and does not require assembly prior to use.</t>
+    <t>Establishes mapping context for a Questionnaire item</t>
+  </si>
+  <si>
+    <t>Specifies a query or other expression that identifies the resource (or set of resources for a repeating item) that should be used to support the population of this Questionnaire or Questionnaire.item on initial population.  When populating the questionnaire, it will set the specified variable name to that resource repetition for use in processing items within the group.</t>
+  </si>
+  <si>
+    <t>Questionnaire.extension:variable</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {variable}
+</t>
+  </si>
+  <si>
+    <t>Variable for processing</t>
+  </si>
+  <si>
+    <t>Variable specifying a logic to generate a variable for use in subsequent logic.  The name of the variable will be added to FHIRPath's context when processing descendants of the element that contains this extension as well as extensions within the same element.</t>
+  </si>
+  <si>
+    <t>Ordering of variable extension declarations is significant as variables declared in one repetition of this extension might be used in subsequent extension repetitions
+For questionnaires, see additional guidance and examples in the [SDC implementation guide](http://hl7.org/fhir/uv/sdc/behavior.html#variable).</t>
   </si>
   <si>
     <t>Questionnaire.modifierExtension</t>
@@ -773,9 +793,6 @@
     <t>If none are specified, then the subject is unlimited.</t>
   </si>
   <si>
-    <t>A Questionnaire SHOULD specify the subject. However, it is optional to support legacy questionnaires.</t>
-  </si>
-  <si>
     <t>One of the resource types defined as part of this version of FHIR.</t>
   </si>
   <si>
@@ -1089,7 +1106,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-que-1:Group items must have nested items, display items cannot have nested items {(type='group' implies item.empty().not()) and (type.trace('type')='display' implies item.trace('item').empty())}que-3:Display items cannot have a "code" asserted {type!='display' or code.empty()}que-4:A question cannot have both answerOption and answerValueSet {answerOption.empty() or answerValueSet.empty()}que-5:Only 'choice' and 'open-choice' items can have answerValueSet {(type ='choice' or type = 'open-choice' or type = 'decimal' or type = 'integer' or type = 'date' or type = 'dateTime' or type = 'time' or type = 'string' or type = 'quantity') or (answerValueSet.empty() and answerOption.empty())}que-6:Required and repeat aren't permitted for display items {type!='display' or (required.empty() and repeats.empty())}que-8:Initial values can't be specified for groups or display items {(type!='group' and type!='display') or initial.empty()}que-9:Read-only can't be specified for "display" items {type!='display' or readOnly.empty()}que-10:Maximum length can only be declared for simple question types {(type in ('boolean' | 'decimal' | 'integer' | 'string' | 'text' | 'url' | 'open-choice')) or maxLength.empty()}que-11:If one or more answerOption is present, initial[x] must be missing {answerOption.empty() or initial.empty()}que-12:If there are more than one enableWhen, enableBehavior must be specified {enableWhen.count() &gt; 2 implies enableBehavior.exists()}que-13:Can only have multiple initial values for repeating items {repeats=true or initial.count() &lt;= 1}sdc-1:An item cannot have an answerExpression if answerOption or answerValueSet is already present. {extension('http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-answerExpression').empty().not() implies (answerOption.empty() and answerValueSet.empty())}que-1a:Group items must have nested items when Questionanire is complete {(type='group' and %resource.status='complete') implies item.empty().not()}que-1b:Groups should have items {type='group' implies item.empty().not()}que-1c:Display items cannot have child items {type='display' implies item.empty()}que-14:Can only have answerConstraint if answerOption, answerValueSet, or answerExpression are present. (This is a warning because other extensions may serve the same purpose) {extension('http://hl7.org/fhir/5.0/StructureDefinition/extension-Questionnaire.item.answerConstraint').exists() implies answerOption.exists() or answerValueSet.exists() or extension('http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-answerExpression').exists()}</t>
+que-1:Group items must have nested items, display items cannot have nested items {(type='group' implies item.empty().not()) and (type.trace('type')='display' implies item.trace('item').empty())}que-3:Display items cannot have a "code" asserted {type!='display' or code.empty()}que-4:A question cannot have both answerOption and answerValueSet {answerOption.empty() or answerValueSet.empty()}que-5:Only 'choice' and 'open-choice' items can have answerValueSet {(type ='choice' or type = 'open-choice' or type = 'decimal' or type = 'integer' or type = 'date' or type = 'dateTime' or type = 'time' or type = 'string' or type = 'quantity') or (answerValueSet.empty() and answerOption.empty())}que-6:Required and repeat aren't permitted for display items {type!='display' or (required.empty() and repeats.empty())}que-8:Initial values can't be specified for groups or display items {(type!='group' and type!='display') or initial.empty()}que-9:Read-only can't be specified for "display" items {type!='display' or readOnly.empty()}que-10:Maximum length can only be declared for simple question types {(type in ('boolean' | 'decimal' | 'integer' | 'string' | 'text' | 'url' | 'open-choice')) or maxLength.empty()}que-11:If one or more answerOption is present, initial[x] must be missing {answerOption.empty() or initial.empty()}que-12:If there are more than one enableWhen, enableBehavior must be specified {enableWhen.count() &gt; 2 implies enableBehavior.exists()}que-13:Can only have multiple initial values for repeating items {repeats=true or initial.count() &lt;= 1}sdc-1:An item cannot have an answerExpression if answerOption or answerValueSet is already present. {extension('http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-answerExpression').empty().not() implies (answerOption.empty() and answerValueSet.empty())}que-1a:Group items must have nested items when Questionanire is complete {(type='group' and %resource.status='complete') implies item.empty().not()}que-1b:Groups should have items {type='group' implies item.empty().not()}que-1c:Display items cannot have child items {type='display' implies item.empty()}que-14:Can only have answerConstraint if answerOption, answerValueSet, or answerExpression are present. (This is a warning because other extensions may serve the same purpose) {extension('http://hl7.org/fhir/5.0/StructureDefinition/extension-Questionnaire.item.answerConstraint').exists() implies answerOption.exists() or answerValueSet.exists() or extension('http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-answerExpression').exists()}sdc-pop-1:An item cannot have both initial.value and initialExpression {initial.empty() or extension('http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-initialExpression').empty()}</t>
   </si>
   <si>
     <t>./form_design/*[self::header or self::footer or self::section]</t>
@@ -1148,29 +1165,136 @@
 </t>
   </si>
   <si>
-    <t>Questionnaire.item.extension:designNote</t>
-  </si>
-  <si>
-    <t>Allows capture of todos, rationale for design decisions, etc.  It can also be used to capture comments about specific groups or questions within it. Allows commentary to be captured during the process of answering a questionnaire (if not already supported by the form design) as well as after the form is completed. Comments are not part of the "data" of the form. If a form prompts for a comment, this should be captured in an answer, not in this element. Formal assessments of the QuestionnaireResponse would use [[[Observation]]].</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.extension:itemOptionalDisplay</t>
-  </si>
-  <si>
-    <t>itemOptionalDisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-optionalDisplay}
+    <t>Questionnaire.item.extension:unit</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {questionnaire-unit}
 </t>
   </si>
   <si>
-    <t>Can suppress from display to user</t>
-  </si>
-  <si>
-    <t>This extension is used when defining high-level questionnaires that will then be used as a basis for 'derived' Questionnaires that are further refined for use in specific organizations or contexts.  If the extension is present and set to 'true', it means that this item should be considered to be 'optional' from an adaptation perspective and that the question can be removed (i.e. not displayed) in derived questionnaires without impacting the validity of the instrument.  Alternatively, the element can be marked as 'hidden' and 'readOnly' and have a value or descendant item values declared using initialValue or initialExpression.  If the element with 'optionalDisplay=true' is marked as 'required=true', then this second approach is the only means to exclude the element from display.</t>
-  </si>
-  <si>
-    <t>If a group or question that contains other groups or questions is marked as "optional", all of its contents are automatically also treated as optional.</t>
+    <t>Unit for numeric answer</t>
+  </si>
+  <si>
+    <t>Provides a computable unit of measure associated with numeric questions to support subsequent computation on responses. This is for use on items of type integer and decimal, and it's purpose is to support converting the integer or decimal answer into a Quantity when extracting the data into a resource.</t>
+  </si>
+  <si>
+    <t>The human-readable unit is conveyed as a display element.  This element is for computation purposes.</t>
+  </si>
+  <si>
+    <t>N/A (MIF-level)</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:itemPopulationContext</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:itemVariable</t>
+  </si>
+  <si>
+    <t>itemVariable</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:initialExpression</t>
+  </si>
+  <si>
+    <t>initialExpression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-initialExpression}
+</t>
+  </si>
+  <si>
+    <t>Expression-determined initial value</t>
+  </si>
+  <si>
+    <t>Initial value for a question answer as determined by an evaluated expression.</t>
+  </si>
+  <si>
+    <t>Initial value is only calculated at the time the QuestionnaireResponse is first generated.  If the expression returns coded data, it **SHALL* return the information as either code or Coding, not CodeableConcept.  If the expression returns elements of type 'code', when the user selects one or more candidates, the code will be matched against the allowed Codings (from answerValueSet, answerOptions, or answerExpression).  In this case, it is an error if there is more than one Coding with the same code.</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:candidateExpression</t>
+  </si>
+  <si>
+    <t>candidateExpression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-candidateExpression}
+</t>
+  </si>
+  <si>
+    <t>Expression for possible answers</t>
+  </si>
+  <si>
+    <t>A FHIRPath or CQL expression, or FHIR Query that resolves to a list of candidate answers for the question item or that establishes context for a group item.  The user may select from among the candidates to choose answers for the question.</t>
+  </si>
+  <si>
+    <t>The results of the expression must correspond to the item type of the question the element appears on or must correspond to a resource, backbone element or complex data type for a group item.  Resources are considered a match for the Reference item type.  Quantity can be a match for decimal and integer items so long as a questionnaire-unit extension is present.  If the expression returns coded data, it **SHALL* return the information as either code or Coding, not CodeableConcept.  If the expression returns elements of type 'code', when the user selects one or more candidates, the code will be matched against the allowed Codings (from answerValueSet, answerOptions, or answerExpresssion).  In this case, it is an error if there is more than one Coding with the same code.</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:contextExpression</t>
+  </si>
+  <si>
+    <t>contextExpression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-contextExpression}
+</t>
+  </si>
+  <si>
+    <t>Expression for information to guide answers</t>
+  </si>
+  <si>
+    <t>A FHIR Query that resolves to one or more resources that can be displayed to the user to help provide context for answering a question. For example, if the question is "Has the patient discussed this issue on any visits in the past year?", the contextExpression might return the set of patient's encounters for the prior 12 month period to help jog the practitioner's memory.</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:itemHidden</t>
+  </si>
+  <si>
+    <t>itemHidden</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:choiceColumn</t>
+  </si>
+  <si>
+    <t>choiceColumn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-choiceColumn}
+</t>
+  </si>
+  <si>
+    <t>Guide for rendering multi-column choices</t>
+  </si>
+  <si>
+    <t>Provides guidelines for rendering multi-column choices.  I.e. when displaying a list of codes (for `choice` or `open-choice` items) or a list of resources (for `reference` items), this extension allows the drop-down to have multiple columns.  For codes, the author can pick additional code system properties to display - such as alternate display names strength or form for drug codes, etc.  For references, the author can choose particular columns from the resource (e.g. first name, last name, specialty, address).</t>
+  </si>
+  <si>
+    <t>Each repetition represents a column to display.</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:isSubject</t>
+  </si>
+  <si>
+    <t>isSubject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-isSubject}
+</t>
+  </si>
+  <si>
+    <t>Marks that this item identifies a different subject</t>
+  </si>
+  <si>
+    <t>If present and true, indicates that the item establishes a different subject for the group in a response.</t>
+  </si>
+  <si>
+    <t>The item type must be "reference" and there can only be one item with this extension in each group.</t>
+  </si>
+  <si>
+    <t>Allows the population process to leverage the fact that the subject for this group and descendants is distinct</t>
   </si>
   <si>
     <t>Questionnaire.item.modifierExtension</t>
@@ -1289,8 +1413,7 @@
     <t>The name of a section, the text of a question or text content for a display item.</t>
   </si>
   <si>
-    <t>When using this element to represent the name of a section, use group type item and also make sure to limit the text element to a short string suitable for display as a section heading.  Group item instructions should be included as a display type item within the group.
-This is optional only to support form assembly situations where the text may be generated from another source.  In an assembled Questionnaire, it should always be present.</t>
+    <t>When using this element to represent the name of a section, use group type item and also make sure to limit the text element to a short string suitable for display as a section heading.  Group item instructions should be included as a display type item within the group.</t>
   </si>
   <si>
     <t>Form Design/designation[context="primary?"/definition/  ./section_instruction/label</t>
@@ -1975,12 +2098,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP75"/>
+  <dimension ref="A1:AP83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.16796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.87109375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.16796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.09765625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3359,7 +3482,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>81</v>
@@ -3501,7 +3624,9 @@
       <c r="M13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>81</v>
@@ -3585,13 +3710,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>81</v>
@@ -3613,17 +3738,15 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N14" t="s" s="2">
         <v>166</v>
       </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>81</v>
@@ -3710,11 +3833,13 @@
         <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3724,29 +3849,27 @@
         <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O15" t="s" s="2">
         <v>172</v>
       </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>81</v>
       </c>
@@ -3794,7 +3917,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3815,7 +3938,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3829,33 +3952,33 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I16" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>175</v>
@@ -3916,31 +4039,31 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
@@ -3951,10 +4074,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3968,7 +4091,7 @@
         <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>81</v>
@@ -3977,19 +4100,19 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -4038,34 +4161,34 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>81</v>
@@ -4073,10 +4196,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4099,18 +4222,20 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
@@ -4158,13 +4283,13 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
@@ -4173,19 +4298,19 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -4193,10 +4318,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4204,7 +4329,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -4219,20 +4344,18 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
       </c>
@@ -4280,7 +4403,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4289,22 +4412,22 @@
         <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>132</v>
+        <v>205</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4341,7 +4464,7 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>208</v>
@@ -4352,7 +4475,9 @@
       <c r="N20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="O20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4409,7 +4534,7 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>101</v>
@@ -4418,10 +4543,10 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>132</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4446,10 +4571,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>90</v>
@@ -4458,21 +4583,21 @@
         <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
       </c>
@@ -4526,7 +4651,7 @@
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
@@ -4538,10 +4663,10 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4555,10 +4680,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4566,22 +4691,22 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>221</v>
@@ -4589,10 +4714,10 @@
       <c r="M22" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>81</v>
       </c>
@@ -4616,13 +4741,13 @@
         <v>81</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -4640,13 +4765,13 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>81</v>
@@ -4655,16 +4780,16 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -4675,10 +4800,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4686,35 +4811,33 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4738,13 +4861,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -4762,10 +4885,10 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>89</v>
@@ -4777,16 +4900,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>81</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -4797,10 +4920,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4808,13 +4931,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G24" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="H24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>81</v>
@@ -4823,7 +4946,7 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>239</v>
@@ -4832,10 +4955,10 @@
         <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4860,13 +4983,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4884,13 +5007,13 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
@@ -4902,13 +5025,13 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>132</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -4919,21 +5042,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>90</v>
@@ -4945,16 +5068,16 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>249</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4980,13 +5103,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5004,13 +5127,13 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
@@ -5022,13 +5145,13 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>255</v>
+        <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -5039,14 +5162,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>81</v>
+        <v>253</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5065,20 +5188,18 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
       </c>
@@ -5126,7 +5247,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5144,13 +5265,13 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -5161,10 +5282,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5175,10 +5296,10 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>81</v>
@@ -5187,18 +5308,20 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
       </c>
@@ -5246,13 +5369,13 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
@@ -5264,13 +5387,13 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -5281,10 +5404,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5295,28 +5418,28 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5366,13 +5489,13 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
@@ -5384,10 +5507,10 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5401,10 +5524,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5415,32 +5538,30 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5488,13 +5609,13 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
@@ -5506,10 +5627,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>199</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5523,10 +5644,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5549,18 +5670,20 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="N30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5584,13 +5707,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>290</v>
+        <v>81</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>291</v>
+        <v>81</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5608,7 +5731,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5626,10 +5749,10 @@
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5643,10 +5766,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5657,28 +5780,28 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K31" t="s" s="2">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5704,13 +5827,13 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>81</v>
+        <v>296</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>81</v>
+        <v>297</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -5728,13 +5851,13 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
@@ -5749,13 +5872,13 @@
         <v>298</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>205</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>81</v>
@@ -5763,14 +5886,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5780,7 +5903,7 @@
         <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>81</v>
@@ -5789,18 +5912,18 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5848,7 +5971,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5866,16 +5989,16 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -5883,14 +6006,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>307</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5900,7 +6023,7 @@
         <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>81</v>
@@ -5909,18 +6032,18 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5968,7 +6091,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5986,16 +6109,16 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>313</v>
+        <v>205</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>81</v>
@@ -6003,10 +6126,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6029,20 +6152,18 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="N34" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>318</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6090,7 +6211,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6108,16 +6229,16 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>81</v>
@@ -6125,10 +6246,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6148,22 +6269,22 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6212,7 +6333,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6230,16 +6351,16 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>81</v>
@@ -6247,10 +6368,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6261,10 +6382,10 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>81</v>
@@ -6273,17 +6394,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6308,13 +6431,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -6332,13 +6455,13 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
@@ -6350,16 +6473,16 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>81</v>
+        <v>332</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>336</v>
+        <v>205</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -6367,10 +6490,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6381,30 +6504,30 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J37" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K37" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6428,13 +6551,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6452,7 +6575,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6461,19 +6584,19 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>343</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6487,10 +6610,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6501,10 +6624,10 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>81</v>
@@ -6513,15 +6636,17 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>193</v>
+        <v>343</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6570,22 +6695,22 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -6619,7 +6744,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6631,13 +6756,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>135</v>
+        <v>352</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>136</v>
+        <v>353</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6676,29 +6801,31 @@
         <v>81</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC39" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6707,7 +6834,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6721,14 +6848,12 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6737,10 +6862,10 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>81</v>
@@ -6749,17 +6874,15 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>355</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>356</v>
+        <v>135</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6796,19 +6919,17 @@
         <v>81</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6843,13 +6964,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>81</v>
@@ -6862,7 +6983,7 @@
         <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
@@ -6871,15 +6992,17 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>144</v>
-      </c>
       <c r="M41" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6928,7 +7051,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6937,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>140</v>
@@ -6949,7 +7072,7 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6963,13 +7086,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>151</v>
+        <v>365</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>81</v>
@@ -6991,17 +7114,15 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>152</v>
+        <v>366</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7050,7 +7171,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7059,7 +7180,7 @@
         <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>140</v>
@@ -7071,7 +7192,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -7085,13 +7206,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>81</v>
@@ -7104,7 +7225,7 @@
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>81</v>
@@ -7113,16 +7234,16 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7172,7 +7293,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7193,7 +7314,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>81</v>
+        <v>373</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7207,46 +7328,44 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D44" t="s" s="2">
-        <v>371</v>
+        <v>81</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>372</v>
+        <v>165</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7294,7 +7413,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7315,7 +7434,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7332,21 +7451,23 @@
         <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>81</v>
@@ -7355,20 +7476,18 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>376</v>
+        <v>170</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>377</v>
+        <v>171</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7416,28 +7535,28 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>382</v>
+        <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7451,12 +7570,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7468,7 +7589,7 @@
         <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
@@ -7477,20 +7598,18 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>103</v>
+        <v>379</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7538,19 +7657,19 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
@@ -7559,7 +7678,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7573,12 +7692,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7587,7 +7708,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7599,20 +7720,18 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>329</v>
+        <v>385</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7636,13 +7755,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7660,7 +7779,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>389</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7669,10 +7788,10 @@
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7681,7 +7800,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7695,24 +7814,26 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="D48" t="s" s="2">
-        <v>395</v>
+        <v>81</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>81</v>
@@ -7721,20 +7842,16 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>391</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7782,28 +7899,28 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>394</v>
+        <v>357</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>400</v>
+        <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>401</v>
+        <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7817,12 +7934,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7834,7 +7953,7 @@
         <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>81</v>
@@ -7843,16 +7962,16 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>193</v>
+        <v>360</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>403</v>
+        <v>361</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>404</v>
+        <v>362</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>405</v>
+        <v>363</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7902,28 +8021,28 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>402</v>
+        <v>357</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7937,24 +8056,26 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>81</v>
@@ -7963,20 +8084,18 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>109</v>
+        <v>398</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -8000,13 +8119,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>412</v>
+        <v>81</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -8024,28 +8143,28 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>407</v>
+        <v>357</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -8059,12 +8178,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8073,31 +8194,31 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8146,7 +8267,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>416</v>
+        <v>357</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8158,7 +8279,7 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>421</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>81</v>
@@ -8167,7 +8288,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -8181,42 +8302,46 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>347</v>
+        <v>411</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8264,19 +8389,19 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>349</v>
+        <v>413</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
@@ -8285,7 +8410,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>350</v>
+        <v>132</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -8299,24 +8424,24 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>81</v>
@@ -8325,18 +8450,20 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8384,28 +8511,28 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>352</v>
+        <v>414</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>140</v>
+        <v>419</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>350</v>
+        <v>421</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -8419,45 +8546,45 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>371</v>
+        <v>81</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>372</v>
+        <v>423</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>373</v>
+        <v>424</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>171</v>
+        <v>425</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>172</v>
+        <v>426</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8506,19 +8633,19 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
@@ -8527,7 +8654,7 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>132</v>
+        <v>427</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -8541,10 +8668,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8552,10 +8679,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8567,18 +8694,20 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>193</v>
+        <v>334</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8602,13 +8731,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8626,16 +8755,16 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
@@ -8647,7 +8776,7 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>415</v>
+        <v>341</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8661,24 +8790,24 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>81</v>
@@ -8687,16 +8816,20 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8720,13 +8853,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>434</v>
+        <v>81</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8744,10 +8877,10 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>89</v>
@@ -8759,13 +8892,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -8779,10 +8912,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8790,13 +8923,13 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>81</v>
@@ -8805,15 +8938,17 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>437</v>
+        <v>199</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8838,52 +8973,52 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="Z57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AA57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>436</v>
-      </c>
       <c r="AG57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>415</v>
+        <v>282</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -8897,10 +9032,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8908,7 +9043,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
@@ -8926,15 +9061,17 @@
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
@@ -8958,13 +9095,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -8982,28 +9119,28 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>81</v>
+        <v>453</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9017,10 +9154,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9031,36 +9168,36 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>232</v>
+        <v>343</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q59" t="s" s="2">
-        <v>453</v>
-      </c>
+      <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9104,28 +9241,28 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -9139,10 +9276,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9156,7 +9293,7 @@
         <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>81</v>
@@ -9165,26 +9302,20 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>457</v>
+        <v>352</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q60" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9228,7 +9359,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>354</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9237,19 +9368,19 @@
         <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>462</v>
+        <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -9263,24 +9394,24 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>81</v>
@@ -9289,20 +9420,18 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>232</v>
+        <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="N61" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
       </c>
@@ -9350,28 +9479,28 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>463</v>
+        <v>357</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>469</v>
+        <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -9385,44 +9514,46 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>471</v>
+        <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9470,28 +9601,28 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>470</v>
+        <v>413</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>476</v>
+        <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>415</v>
+        <v>132</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9500,15 +9631,15 @@
         <v>81</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9516,13 +9647,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>81</v>
@@ -9531,16 +9662,16 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>478</v>
+        <v>199</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9590,28 +9721,28 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>482</v>
+        <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9625,10 +9756,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9636,13 +9767,13 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>81</v>
@@ -9651,17 +9782,15 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>338</v>
+        <v>109</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9686,13 +9815,13 @@
         <v>81</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>81</v>
+        <v>474</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
@@ -9710,16 +9839,16 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>482</v>
+        <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>101</v>
@@ -9731,7 +9860,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9745,10 +9874,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9756,7 +9885,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>89</v>
@@ -9771,13 +9900,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>193</v>
+        <v>476</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>347</v>
+        <v>477</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>348</v>
+        <v>478</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9804,13 +9933,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>81</v>
+        <v>479</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9828,19 +9957,19 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>349</v>
+        <v>475</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>81</v>
+        <v>481</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>81</v>
@@ -9849,7 +9978,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>350</v>
+        <v>454</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9863,24 +9992,24 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>81</v>
@@ -9889,16 +10018,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>424</v>
+        <v>483</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>425</v>
+        <v>484</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>171</v>
+        <v>485</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9924,13 +10053,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>81</v>
+        <v>484</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>81</v>
+        <v>486</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9948,19 +10077,19 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>352</v>
+        <v>482</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>81</v>
+        <v>487</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -9969,7 +10098,7 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>350</v>
+        <v>454</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -9983,50 +10112,50 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>371</v>
+        <v>81</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>134</v>
+        <v>238</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>372</v>
+        <v>489</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>373</v>
+        <v>490</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q67" s="2"/>
+      <c r="Q67" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="R67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10070,28 +10199,28 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>374</v>
+        <v>488</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>81</v>
+        <v>493</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>81</v>
+        <v>494</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>132</v>
+        <v>454</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10105,10 +10234,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10116,7 +10245,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>89</v>
@@ -10131,87 +10260,91 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>492</v>
+        <v>238</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="N68" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q68" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="R68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>491</v>
-      </c>
       <c r="AG68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>81</v>
+        <v>493</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10225,10 +10358,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10251,24 +10384,24 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q69" t="s" s="2">
-        <v>500</v>
-      </c>
+      <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10312,7 +10445,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10321,19 +10454,19 @@
         <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -10347,10 +10480,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10361,10 +10494,10 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>81</v>
@@ -10373,20 +10506,18 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>338</v>
+        <v>510</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
@@ -10434,28 +10565,28 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>81</v>
+        <v>515</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10464,15 +10595,15 @@
         <v>81</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>81</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10486,7 +10617,7 @@
         <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>81</v>
@@ -10495,15 +10626,17 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>193</v>
+        <v>517</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>347</v>
+        <v>518</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10552,7 +10685,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>349</v>
+        <v>516</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10561,19 +10694,19 @@
         <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>81</v>
+        <v>522</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>350</v>
+        <v>454</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10587,14 +10720,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10604,7 +10737,7 @@
         <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>81</v>
@@ -10613,16 +10746,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>134</v>
+        <v>343</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>424</v>
+        <v>524</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>425</v>
+        <v>525</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>171</v>
+        <v>526</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10672,7 +10805,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>352</v>
+        <v>523</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10681,10 +10814,10 @@
         <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>81</v>
@@ -10693,7 +10826,7 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>350</v>
+        <v>454</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10707,46 +10840,42 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>371</v>
+        <v>81</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10794,19 +10923,19 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>81</v>
@@ -10815,7 +10944,7 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>132</v>
+        <v>355</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -10829,24 +10958,24 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>81</v>
@@ -10855,16 +10984,16 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>511</v>
+        <v>134</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>512</v>
+        <v>463</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>513</v>
+        <v>464</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>514</v>
+        <v>177</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10890,13 +11019,13 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -10914,28 +11043,28 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>510</v>
+        <v>357</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>515</v>
+        <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -10949,14 +11078,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10966,28 +11095,28 @@
         <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I75" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I75" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J75" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>517</v>
+        <v>411</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>518</v>
+        <v>412</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>519</v>
+        <v>177</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>520</v>
+        <v>178</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11036,7 +11165,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>516</v>
+        <v>413</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11045,32 +11174,998 @@
         <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>521</v>
+        <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK75" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP75" t="s" s="2">
+      <c r="AK76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q77" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="R77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP75">
+  <autoFilter ref="A1:AP83">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11080,7 +12175,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI82">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-organization.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3219" uniqueCount="561">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T18:16:37+00:00</t>
+    <t>2026-02-06T16:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -511,17 +511,12 @@
     <t>launchContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-launchContext}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/ror/StructureDefinition/ror-launchcontext}
 </t>
   </si>
   <si>
-    <t>Context resources needed for Questionnaire</t>
-  </si>
-  <si>
-    <t>Resources that provide context for form processing logic (pre-population, flow-control, drop-down selection, etc.) when creating/displaying/editing a QuestionnaireResponse.</t>
-  </si>
-  <si>
-    <t>3 of these launch contexts are aligned with the existing SMART on FHIR "launch" contexts.</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource; ror-structure: Location, HealthcareServive, Organization {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy')) and (extension('name').value.where(code='ror-structure' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Location' or value='HealthcareService' or value='Organization'))}</t>
   </si>
   <si>
     <t>Questionnaire.extension:itemPopulationContext</t>
@@ -3121,7 +3116,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>80</v>
@@ -3601,10 +3596,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>90</v>
@@ -3619,14 +3614,12 @@
         <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>81</v>
@@ -3684,10 +3677,10 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>81</v>
@@ -3710,13 +3703,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>81</v>
@@ -3738,13 +3731,13 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3830,13 +3823,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>81</v>
@@ -3858,16 +3851,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3952,14 +3945,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3981,16 +3974,16 @@
         <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -4039,7 +4032,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4074,10 +4067,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4103,16 +4096,16 @@
         <v>103</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -4161,7 +4154,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4173,19 +4166,19 @@
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AK17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
@@ -4196,10 +4189,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4222,19 +4215,19 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -4283,7 +4276,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4301,16 +4294,16 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -4318,10 +4311,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4344,16 +4337,16 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4403,7 +4396,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4418,16 +4411,16 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4438,10 +4431,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4464,19 +4457,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4525,7 +4518,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4534,7 +4527,7 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>101</v>
@@ -4560,10 +4553,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4586,16 +4579,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4645,7 +4638,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4663,10 +4656,10 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4680,10 +4673,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4706,17 +4699,17 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4765,7 +4758,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4783,10 +4776,10 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4800,10 +4793,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4829,13 +4822,13 @@
         <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4861,14 +4854,14 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="Y23" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4885,7 +4878,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>89</v>
@@ -4900,16 +4893,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -4920,10 +4913,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4946,19 +4939,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -5007,7 +5000,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5025,13 +5018,13 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>132</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -5042,10 +5035,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5071,13 +5064,13 @@
         <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5103,13 +5096,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5127,7 +5120,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5145,10 +5138,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -5162,14 +5155,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5188,16 +5181,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5247,7 +5240,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5265,13 +5258,13 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -5282,10 +5275,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5308,19 +5301,19 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5369,7 +5362,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5387,13 +5380,13 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -5404,10 +5397,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5430,16 +5423,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5489,7 +5482,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5507,10 +5500,10 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5524,10 +5517,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5550,16 +5543,16 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5609,7 +5602,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5627,10 +5620,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5644,10 +5637,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5670,19 +5663,19 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5731,7 +5724,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5749,10 +5742,10 @@
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5766,10 +5759,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5792,16 +5785,16 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5827,14 +5820,14 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="Y31" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5851,7 +5844,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5869,10 +5862,10 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5886,10 +5879,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5912,16 +5905,16 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5971,7 +5964,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5989,16 +5982,16 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="AO32" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6006,14 +5999,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6032,17 +6025,17 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -6091,7 +6084,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6109,16 +6102,16 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>81</v>
@@ -6126,10 +6119,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6152,16 +6145,16 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6211,7 +6204,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6229,16 +6222,16 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>81</v>
@@ -6246,10 +6239,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6272,19 +6265,19 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6333,7 +6326,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6351,16 +6344,16 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>81</v>
@@ -6368,10 +6361,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6394,19 +6387,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6455,7 +6448,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6473,16 +6466,16 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -6490,10 +6483,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6516,17 +6509,17 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6551,14 +6544,14 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="Y37" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6575,7 +6568,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6596,7 +6589,7 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6610,10 +6603,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6636,16 +6629,16 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6695,7 +6688,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6704,19 +6697,19 @@
         <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AJ38" t="s" s="2">
+      <c r="AL38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6730,10 +6723,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6756,13 +6749,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6813,7 +6806,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6834,7 +6827,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6848,10 +6841,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6929,7 +6922,7 @@
         <v>138</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6964,13 +6957,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>81</v>
@@ -6992,16 +6985,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7051,7 +7044,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7086,13 +7079,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>81</v>
@@ -7114,7 +7107,7 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>144</v>
@@ -7171,7 +7164,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7206,13 +7199,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>81</v>
@@ -7234,16 +7227,16 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7293,7 +7286,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7314,7 +7307,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7328,13 +7321,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>81</v>
@@ -7356,13 +7349,13 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7413,7 +7406,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7448,13 +7441,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>81</v>
@@ -7476,16 +7469,16 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7535,7 +7528,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7570,13 +7563,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>81</v>
@@ -7598,16 +7591,16 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7657,7 +7650,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7692,13 +7685,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>81</v>
@@ -7720,16 +7713,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7779,7 +7772,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7814,13 +7807,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>81</v>
@@ -7842,13 +7835,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7899,7 +7892,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7934,13 +7927,13 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>81</v>
@@ -7962,16 +7955,16 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8021,7 +8014,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8056,13 +8049,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>81</v>
@@ -8084,16 +8077,16 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8143,7 +8136,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8178,13 +8171,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>81</v>
@@ -8206,19 +8199,19 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8267,7 +8260,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8302,14 +8295,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8331,16 +8324,16 @@
         <v>134</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8389,7 +8382,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8424,10 +8417,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8450,19 +8443,19 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8511,7 +8504,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>89</v>
@@ -8523,16 +8516,16 @@
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -8546,10 +8539,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8575,16 +8568,16 @@
         <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8633,7 +8626,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8654,7 +8647,7 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -8668,10 +8661,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8694,19 +8687,19 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8731,14 +8724,14 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="Y55" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8755,7 +8748,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8764,7 +8757,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
@@ -8776,7 +8769,7 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8790,14 +8783,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8816,19 +8809,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8877,7 +8870,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8892,13 +8885,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -8912,10 +8905,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8938,16 +8931,16 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8997,7 +8990,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9012,13 +9005,13 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -9032,10 +9025,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9061,16 +9054,16 @@
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9095,13 +9088,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -9119,7 +9112,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>89</v>
@@ -9134,13 +9127,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9154,10 +9147,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9180,19 +9173,19 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9241,7 +9234,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9253,7 +9246,7 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9262,7 +9255,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -9276,10 +9269,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9302,13 +9295,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9359,7 +9352,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9380,7 +9373,7 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -9394,14 +9387,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9423,13 +9416,13 @@
         <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9479,7 +9472,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9500,7 +9493,7 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -9514,14 +9507,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9543,16 +9536,16 @@
         <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9601,7 +9594,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9636,10 +9629,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9662,16 +9655,16 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9721,7 +9714,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>89</v>
@@ -9742,7 +9735,7 @@
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9756,10 +9749,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9785,10 +9778,10 @@
         <v>109</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9815,13 +9808,13 @@
         <v>81</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
@@ -9839,7 +9832,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>89</v>
@@ -9860,7 +9853,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9874,10 +9867,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9900,13 +9893,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9933,13 +9926,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9957,7 +9950,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>89</v>
@@ -9966,7 +9959,7 @@
         <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>101</v>
@@ -9978,7 +9971,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9992,10 +9985,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10021,13 +10014,13 @@
         <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10053,14 +10046,14 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>486</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10077,7 +10070,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10086,7 +10079,7 @@
         <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>101</v>
@@ -10098,7 +10091,7 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -10112,10 +10105,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10138,23 +10131,23 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q67" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="R67" t="s" s="2">
         <v>81</v>
@@ -10199,7 +10192,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10208,19 +10201,19 @@
         <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10234,10 +10227,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10260,26 +10253,26 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="P68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q68" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="O68" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q68" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="R68" t="s" s="2">
         <v>81</v>
       </c>
@@ -10323,7 +10316,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10332,19 +10325,19 @@
         <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10358,10 +10351,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10384,19 +10377,19 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10445,7 +10438,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10454,19 +10447,19 @@
         <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -10480,10 +10473,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10506,16 +10499,16 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10565,7 +10558,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10574,19 +10567,19 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10600,10 +10593,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10626,16 +10619,16 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10685,7 +10678,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10694,19 +10687,19 @@
         <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10720,10 +10713,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10746,16 +10739,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10805,7 +10798,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10814,7 +10807,7 @@
         <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>101</v>
@@ -10826,7 +10819,7 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10840,10 +10833,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10866,13 +10859,13 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10923,7 +10916,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10944,7 +10937,7 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -10958,14 +10951,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10987,13 +10980,13 @@
         <v>134</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11043,7 +11036,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11064,7 +11057,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -11078,14 +11071,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11107,16 +11100,16 @@
         <v>134</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11165,7 +11158,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11200,10 +11193,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11226,16 +11219,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11261,13 +11254,13 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -11285,7 +11278,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>89</v>
@@ -11306,7 +11299,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -11320,10 +11313,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11346,23 +11339,23 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q77" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="R77" t="s" s="2">
         <v>81</v>
@@ -11407,7 +11400,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11428,7 +11421,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -11442,10 +11435,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11468,19 +11461,19 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -11529,7 +11522,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11538,7 +11531,7 @@
         <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>101</v>
@@ -11550,7 +11543,7 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -11564,10 +11557,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11590,13 +11583,13 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11647,7 +11640,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11668,7 +11661,7 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -11682,14 +11675,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11711,13 +11704,13 @@
         <v>134</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11767,7 +11760,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11788,7 +11781,7 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -11802,14 +11795,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11831,16 +11824,16 @@
         <v>134</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>81</v>
@@ -11889,7 +11882,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11924,10 +11917,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11950,16 +11943,16 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11985,13 +11978,13 @@
         <v>81</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12009,7 +12002,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>89</v>
@@ -12024,13 +12017,13 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12044,10 +12037,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12073,16 +12066,16 @@
         <v>82</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -12131,7 +12124,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12140,19 +12133,19 @@
         <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-organization.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T16:44:46+00:00</t>
+    <t>2026-02-09T14:48:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
